--- a/ttl_long/AdHoc_Net_17.xlsx
+++ b/ttl_long/AdHoc_Net_17.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>288</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>156</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>291</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>229</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>276</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>514</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>507</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>456</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>700</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>532</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>318</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>583</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>823</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>791</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>982</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>178</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>1118</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>1148</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>145</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1141</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1284</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>1197</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1335</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1461</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1424</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1601</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1596</t>
         </is>
       </c>
     </row>
@@ -987,199 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1136</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1542</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1658</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1577</t>
+          <t>1567</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D128"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1249,7 +1062,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1271,7 +1084,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1288,12 +1101,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1315,7 +1128,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1337,7 +1150,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1354,7 +1167,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1381,7 +1194,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1403,7 +1216,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1420,12 +1233,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1442,12 +1255,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1469,7 +1282,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1486,12 +1299,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1508,12 +1321,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1530,12 +1343,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1552,12 +1365,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1574,12 +1387,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1596,12 +1409,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1618,12 +1431,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1640,12 +1453,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1662,12 +1475,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1684,12 +1497,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1706,12 +1519,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1728,12 +1541,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1750,12 +1563,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1772,7 +1585,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1794,12 +1607,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1816,12 +1629,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1838,12 +1651,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1860,12 +1673,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1882,12 +1695,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1904,12 +1717,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1926,12 +1739,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1948,12 +1761,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1970,12 +1783,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1992,12 +1805,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2014,12 +1827,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2036,7 +1849,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2058,12 +1871,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2080,12 +1893,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2102,7 +1915,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2124,12 +1937,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2146,12 +1959,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2168,12 +1981,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2190,12 +2003,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2212,12 +2025,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2239,7 +2052,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2261,7 +2074,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2278,12 +2091,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2305,7 +2118,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2322,12 +2135,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2344,12 +2157,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2366,12 +2179,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2388,12 +2201,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2410,12 +2223,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2432,12 +2245,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2459,7 +2272,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2476,12 +2289,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2498,12 +2311,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2520,12 +2333,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2542,12 +2355,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2564,12 +2377,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2586,12 +2399,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2608,12 +2421,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2630,12 +2443,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2652,12 +2465,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2674,12 +2487,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2696,12 +2509,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2718,12 +2531,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2740,12 +2553,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2762,7 +2575,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2784,12 +2597,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2806,12 +2619,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2828,12 +2641,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2850,12 +2663,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2872,12 +2685,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2894,12 +2707,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2916,12 +2729,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,12 +2751,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2960,7 +2773,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2982,12 +2795,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3004,12 +2817,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3026,12 +2839,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3040,974 +2853,6 @@
         </is>
       </c>
       <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4056,7 +2901,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -4082,7 +2927,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_17.xlsx
+++ b/ttl_long/AdHoc_Net_17.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>247</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>212</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>184</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>207</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>265</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>379</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>314</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>304</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>412</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>536</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>424</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>471</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>699</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>177</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>554</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>594</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>803</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>820</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>344</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>761</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>952</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>838</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>909</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1057</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>979</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1020</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1037</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>194</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1032</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>313</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1148</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1204</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1324</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,148 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1232</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1545</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1062,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1084,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1106,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1128,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1150,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1172,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1189,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1216,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1238,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1260,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1282,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1304,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1326,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1348,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1370,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1392,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1409,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1436,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1453,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1475,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1497,7 +1633,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1519,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1541,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1563,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1585,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1607,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1629,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1651,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1673,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1695,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1717,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1739,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1761,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1783,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1805,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1827,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1849,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1871,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1893,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1915,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1937,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1959,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1981,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2008,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2030,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2052,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2074,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2096,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2118,7 +2254,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2135,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2157,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2179,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2206,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2223,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2245,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2272,7 +2408,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2289,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2311,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2333,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2355,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2377,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2399,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2421,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2443,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2465,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2487,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2509,7 +2645,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2531,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2553,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2575,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2597,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2619,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2641,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2663,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2685,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2707,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2729,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2751,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2773,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2795,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2817,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2839,20 +2975,834 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2901,7 +3851,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -2921,7 +3871,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_17.xlsx
+++ b/ttl_long/AdHoc_Net_17.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>98</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>159</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>175</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>243</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>171</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>172</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>322</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>281</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>371</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>509</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>527</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>345</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>510</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>604</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>691</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>739</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>761</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>861</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>258</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>879</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>879</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>996</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1015</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>996</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1057</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1037</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>295</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1133</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1188</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1236</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1235</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1338</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1375</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1400</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1426</t>
+          <t>1563</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>115</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1445</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1535</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1615</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1664</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1457,7 +1457,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1479,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1501,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2293,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,7 +2447,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2777,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,7 +2887,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,7 +2931,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3701,7 +3701,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3715,94 +3715,6 @@
         </is>
       </c>
       <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
